--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/3-Calculations/MethodTables.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/3-Calculations/MethodTables.xlsx
@@ -809,7 +809,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>"while (condition) statement" and "for (init; condition; update) statement" repeat statements, and "return" leaves the method from inside a loop. Write "i += 1" instead of the deprecated "i++". The BEX language has no "break", "continue" or "do ... while": put the exit into the loop condition, or use the BREAK and CONTINUE operations of a TBasic table.</t>
+          <t>"while (condition) statement" and "for (init; condition; update) statement" repeat statements, and "return" leaves the method from inside a loop. Write "i += 1" to step a counter: the BEX language has no "++", "--", "break", "continue" or "do ... while". Put the exit into the loop condition, or use the BREAK and CONTINUE operations of a TBasic table.</t>
         </is>
       </c>
     </row>

--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/3-Calculations/MethodTables.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/3-Calculations/MethodTables.xlsx
@@ -809,7 +809,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>"while (condition) statement" and "for (init; condition; update) statement" repeat statements, and "return" leaves the method from inside a loop. Write "i += 1" to step a counter: the BEX language has no "++", "--", "break", "continue" or "do ... while". Put the exit into the loop condition, or use the BREAK and CONTINUE operations of a TBasic table.</t>
+          <t>"while (condition) statement" and "for (init; condition; update) statement" repeat statements, and "return" leaves the method from inside a loop. Write "i += 1" instead of the deprecated "i++". The BEX language has no "break", "continue" or "do ... while": put the exit into the loop condition, or use the BREAK and CONTINUE operations of a TBasic table.</t>
         </is>
       </c>
     </row>
